--- a/output/2026-09-19/enriched_analysis.xlsx
+++ b/output/2026-09-19/enriched_analysis.xlsx
@@ -1125,12 +1125,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1142,177 +1142,177 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I4" t="n">
-        <v>91.05</v>
+        <v>654.2</v>
       </c>
       <c r="J4" t="n">
-        <v>75.68000000000001</v>
+        <v>619.77</v>
       </c>
       <c r="K4" t="n">
-        <v>20.3</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
-        <v>74.84999999999999</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>3.14</v>
+        <v>4.88</v>
       </c>
       <c r="N4" t="n">
+        <v>35</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1207</v>
+      </c>
+      <c r="R4" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>21</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="U4" t="n">
+        <v>23</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>581.76</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>515.16</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>619.774620153463</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>17-06-2026</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>93</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>94</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6908288</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9395107</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>23722839</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>28676708</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>36961788</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6908288</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>23722839</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2377</v>
-      </c>
-      <c r="R4" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>62</v>
-      </c>
-      <c r="U4" t="n">
-        <v>77</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W4" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Y4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>185</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>75.6844038997483</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>08-09-2026</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
-        </is>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>31393588</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>31393588</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>31393588</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>31393588</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>31393588</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1</v>
-      </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>0.2912</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1324,87 +1324,87 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
         <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>69.98999999999999</v>
+        <v>91.05</v>
       </c>
       <c r="J5" t="n">
-        <v>74.56</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.1</v>
+        <v>20.3</v>
       </c>
       <c r="L5" t="n">
-        <v>72.56999999999999</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>1.85</v>
+        <v>3.14</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.898</v>
+        <v>0.132</v>
       </c>
       <c r="Q5" t="n">
-        <v>206</v>
+        <v>2377</v>
       </c>
       <c r="R5" t="n">
-        <v>8.76</v>
+        <v>20.8</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>-3</v>
       </c>
       <c r="T5" t="n">
-        <v>27.97</v>
+        <v>62</v>
       </c>
       <c r="U5" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="V5" t="n">
-        <v>2.73</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>13.7</v>
+        <v>15.8</v>
       </c>
       <c r="X5" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>61.72</v>
+        <v>62.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>52.36</v>
+        <v>46.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>58.2</v>
+        <v>185</v>
       </c>
       <c r="AD5" t="n">
-        <v>74.56036417156598</v>
+        <v>75.6844038997483</v>
       </c>
       <c r="AE5" t="n">
-        <v>-6.1</v>
+        <v>20.3</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1418,63 +1418,63 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="AM5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AP5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AR5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>7368443</v>
+        <v>31393588</v>
       </c>
       <c r="AU5" t="n">
-        <v>11712828</v>
+        <v>31393588</v>
       </c>
       <c r="AV5" t="n">
-        <v>18541224</v>
+        <v>31393588</v>
       </c>
       <c r="AW5" t="n">
-        <v>18541224</v>
+        <v>31393588</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>11712828</v>
+        <v>31393588</v>
       </c>
       <c r="AZ5" t="n">
         <v>1</v>
@@ -1671,12 +1671,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1688,157 +1688,157 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>72.56999999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>206</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="S7" t="n">
+        <v>17</v>
+      </c>
+      <c r="T7" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="U7" t="n">
+        <v>17</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W7" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>61.72</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>52.36</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>74.56036417156598</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="AK7" t="n">
         <v>25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>102.63</v>
-      </c>
-      <c r="J7" t="n">
-        <v>92.77</v>
-      </c>
-      <c r="K7" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="L7" t="n">
-        <v>70.88</v>
-      </c>
-      <c r="M7" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2635</v>
-      </c>
-      <c r="R7" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>14</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-14</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="W7" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Y7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>93.94</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>92.31999999999999</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>92.82585700497917</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="AK7" t="n">
-        <v>30</v>
       </c>
       <c r="AL7" t="n">
         <v>33</v>
       </c>
       <c r="AM7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AS7" t="n">
-        <v>12179344</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>12179344</v>
+        <v>7368443</v>
       </c>
       <c r="AU7" t="n">
-        <v>47798301</v>
+        <v>11712828</v>
       </c>
       <c r="AV7" t="n">
-        <v>98005447</v>
+        <v>18541224</v>
       </c>
       <c r="AW7" t="n">
-        <v>98005447</v>
+        <v>18541224</v>
       </c>
       <c r="AX7" t="n">
-        <v>12179344</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47798301</v>
+        <v>11712828</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
@@ -1847,22 +1847,22 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.2548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1873,163 +1873,163 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
       </c>
       <c r="H8" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>654.2</v>
+        <v>102.63</v>
       </c>
       <c r="J8" t="n">
-        <v>617.65</v>
+        <v>92.77</v>
       </c>
       <c r="K8" t="n">
-        <v>5.9</v>
+        <v>10.6</v>
       </c>
       <c r="L8" t="n">
-        <v>64.68000000000001</v>
+        <v>70.88</v>
       </c>
       <c r="M8" t="n">
-        <v>4.46</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N8" t="n">
+        <v>6</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2635</v>
+      </c>
+      <c r="R8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>14</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-14</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="W8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>93.94</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>92.82585700497917</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Mature — Wait for Pullback</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL8" t="n">
         <v>33</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1207</v>
-      </c>
-      <c r="R8" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>21</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>23</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-110</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>581.76</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>515.16</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>617.650011076037</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>17-06-2026</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="AK8" t="n">
-        <v>91</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>94</v>
       </c>
       <c r="AM8" t="n">
         <v>3</v>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
         <v>5</v>
       </c>
-      <c r="AP8" t="n">
-        <v>19</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>2733734</v>
+        <v>12179344</v>
       </c>
       <c r="AT8" t="n">
-        <v>5220553</v>
+        <v>12179344</v>
       </c>
       <c r="AU8" t="n">
-        <v>19548285</v>
+        <v>47798301</v>
       </c>
       <c r="AV8" t="n">
-        <v>24502154</v>
+        <v>98005447</v>
       </c>
       <c r="AW8" t="n">
-        <v>32787234</v>
+        <v>98005447</v>
       </c>
       <c r="AX8" t="n">
-        <v>2733734</v>
+        <v>12179344</v>
       </c>
       <c r="AY8" t="n">
-        <v>19548285</v>
+        <v>47798301</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.1398</v>
+        <v>0.2548</v>
       </c>
     </row>
     <row r="9">
@@ -6031,12 +6031,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BERGER PAINTS (I) LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -6048,91 +6048,91 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I31" t="n">
-        <v>458.65</v>
+        <v>51.9</v>
       </c>
       <c r="J31" t="n">
-        <v>489.56</v>
+        <v>56.04</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.3</v>
+        <v>-7.4</v>
       </c>
       <c r="L31" t="n">
-        <v>75</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>4.84</v>
+        <v>2.19</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.487</v>
       </c>
       <c r="Q31" t="n">
-        <v>53479</v>
+        <v>450</v>
       </c>
       <c r="R31" t="n">
-        <v>45.3</v>
+        <v>11.2</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="T31" t="n">
-        <v>562</v>
+        <v>21</v>
       </c>
       <c r="U31" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V31" t="n">
-        <v>3.16</v>
+        <v>1.22</v>
       </c>
       <c r="W31" t="n">
-        <v>22.9</v>
+        <v>12</v>
       </c>
       <c r="X31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="Y31" t="b">
         <v>1</v>
       </c>
       <c r="Z31" t="n">
-        <v>17</v>
+        <v>3.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>504.63</v>
+        <v>56.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>494.86</v>
+        <v>58.31</v>
       </c>
       <c r="AC31" t="n">
-        <v>13.4</v>
+        <v>-14.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>489.5623319654733</v>
+        <v>56.76403555898796</v>
       </c>
       <c r="AE31" t="n">
-        <v>-6.3</v>
+        <v>-8.6</v>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -6147,31 +6147,31 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL31" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="AM31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AP31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AQ31" t="n">
         <v>5</v>
@@ -6180,34 +6180,34 @@
         <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2958659</v>
       </c>
       <c r="AT31" t="n">
-        <v>48436318</v>
+        <v>2958659</v>
       </c>
       <c r="AU31" t="n">
-        <v>48436318</v>
+        <v>2958659</v>
       </c>
       <c r="AV31" t="n">
-        <v>48436318</v>
+        <v>27048290</v>
       </c>
       <c r="AW31" t="n">
-        <v>48436318</v>
+        <v>27048290</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>2958659</v>
       </c>
       <c r="AY31" t="n">
-        <v>48436318</v>
+        <v>2958659</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BA31" t="n">
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -6395,16 +6395,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>BERGER PAINTS (I) LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -6412,87 +6412,91 @@
         </is>
       </c>
       <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="n">
         <v>16</v>
-      </c>
-      <c r="F33" t="n">
-        <v>8</v>
       </c>
       <c r="G33" t="n">
         <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>12.46</v>
+        <v>458.65</v>
       </c>
       <c r="J33" t="n">
-        <v>12.86</v>
+        <v>489.56</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.1</v>
+        <v>-6.3</v>
       </c>
       <c r="L33" t="n">
-        <v>69.12</v>
+        <v>75</v>
       </c>
       <c r="M33" t="n">
-        <v>2.35</v>
+        <v>4.84</v>
       </c>
       <c r="N33" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.668</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>352</v>
+        <v>53479</v>
       </c>
       <c r="R33" t="n">
-        <v>1134</v>
+        <v>45.3</v>
       </c>
       <c r="S33" t="n">
-        <v>-61</v>
-      </c>
-      <c r="T33" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>562</v>
+      </c>
       <c r="U33" t="n">
-        <v>-98</v>
+        <v>8</v>
       </c>
       <c r="V33" t="n">
-        <v>0.01</v>
+        <v>3.16</v>
       </c>
       <c r="W33" t="n">
-        <v>2.46</v>
+        <v>22.9</v>
       </c>
       <c r="X33" t="n">
-        <v>0.44</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y33" t="b">
         <v>1</v>
       </c>
-      <c r="Z33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>17</v>
+      </c>
       <c r="AA33" t="n">
-        <v>11.92</v>
+        <v>504.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>13.23</v>
+        <v>494.86</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.1</v>
+        <v>13.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>12.81726116235803</v>
+        <v>489.5623319654733</v>
       </c>
       <c r="AE33" t="n">
-        <v>-2.8</v>
+        <v>-6.3</v>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -6507,82 +6511,82 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AK33" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AM33" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AN33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AP33" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AR33" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AS33" t="n">
-        <v>2483137</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>7077674</v>
+        <v>48436318</v>
       </c>
       <c r="AU33" t="n">
-        <v>13663449</v>
+        <v>48436318</v>
       </c>
       <c r="AV33" t="n">
-        <v>24036761</v>
+        <v>48436318</v>
       </c>
       <c r="AW33" t="n">
-        <v>24036761</v>
+        <v>48436318</v>
       </c>
       <c r="AX33" t="n">
-        <v>2483137</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>13663449</v>
+        <v>48436318</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BA33" t="n">
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.1817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -6590,157 +6594,153 @@
         </is>
       </c>
       <c r="E34" t="n">
+        <v>16</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="J34" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>69.12</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N34" t="n">
+        <v>24</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>17-09-2026</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>352</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1134</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-61</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="n">
+        <v>-98</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Y34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>12.81726116235803</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>10-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>17-09-2026</t>
+        </is>
+      </c>
+      <c r="AK34" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM34" t="n">
         <v>2</v>
       </c>
-      <c r="F34" t="n">
-        <v>12</v>
-      </c>
-      <c r="G34" t="n">
-        <v>17</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>125.64</v>
-      </c>
-      <c r="J34" t="n">
-        <v>105.19</v>
-      </c>
-      <c r="K34" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="L34" t="n">
-        <v>67.15000000000001</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5072</v>
-      </c>
-      <c r="R34" t="n">
-        <v>33</v>
-      </c>
-      <c r="S34" t="n">
-        <v>-25</v>
-      </c>
-      <c r="T34" t="n">
-        <v>71</v>
-      </c>
-      <c r="U34" t="n">
-        <v>-11</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W34" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>69</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>111.36</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>112.09</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>105.19</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>86</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>86</v>
-      </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AR34" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2483137</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>7077674</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>13663449</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>24036761</v>
       </c>
       <c r="AW34" t="n">
-        <v>78892500</v>
+        <v>24036761</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>2483137</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>13663449</v>
       </c>
       <c r="AZ34" t="n">
         <v>1</v>
@@ -6749,22 +6749,22 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>0.1817</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -6772,87 +6772,85 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F35" t="n">
+        <v>19</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>718.8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>799.47</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="G35" t="n">
-        <v>9</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>421.7</v>
-      </c>
-      <c r="J35" t="n">
-        <v>446.04</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="M35" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="N35" t="n">
-        <v>8</v>
-      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>17-09-2026</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.535</v>
+        <v>0.195</v>
       </c>
       <c r="Q35" t="n">
-        <v>3616</v>
+        <v>728</v>
       </c>
       <c r="R35" t="n">
-        <v>25.3</v>
+        <v>13.2</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>185</v>
       </c>
       <c r="T35" t="n">
-        <v>127</v>
+        <v>11.55</v>
       </c>
       <c r="U35" t="n">
-        <v>-14</v>
+        <v>204</v>
       </c>
       <c r="V35" t="n">
-        <v>6.41</v>
+        <v>6.84</v>
       </c>
       <c r="W35" t="n">
-        <v>9.890000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
-        <v>21</v>
+        <v>16.07</v>
       </c>
       <c r="AA35" t="n">
-        <v>438.71</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>431.95</v>
-      </c>
+        <v>729.78</v>
+      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
-        <v>12.4</v>
+        <v>-20.9</v>
       </c>
       <c r="AD35" t="n">
-        <v>454.2782298941436</v>
+        <v>799.4678184281843</v>
       </c>
       <c r="AE35" t="n">
-        <v>-7.2</v>
+        <v>-10.1</v>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
@@ -6871,7 +6869,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -6880,52 +6878,52 @@
         </is>
       </c>
       <c r="AK35" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="AL35" t="n">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="AM35" t="n">
         <v>2</v>
       </c>
       <c r="AN35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AQ35" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AR35" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AS35" t="n">
-        <v>91162330</v>
+        <v>1751854</v>
       </c>
       <c r="AT35" t="n">
-        <v>91162330</v>
+        <v>1751854</v>
       </c>
       <c r="AU35" t="n">
-        <v>91162330</v>
+        <v>1751854</v>
       </c>
       <c r="AV35" t="n">
-        <v>274696140</v>
+        <v>1751854</v>
       </c>
       <c r="AW35" t="n">
-        <v>274696140</v>
+        <v>5375657</v>
       </c>
       <c r="AX35" t="n">
-        <v>91162330</v>
+        <v>1751854</v>
       </c>
       <c r="AY35" t="n">
-        <v>91162330</v>
+        <v>1751854</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA35" t="n">
         <v>0</v>
@@ -6937,16 +6935,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6954,335 +6952,339 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>128.15</v>
+        <v>125.64</v>
       </c>
       <c r="J36" t="n">
-        <v>132.2</v>
+        <v>105.19</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.1</v>
+        <v>19.4</v>
       </c>
       <c r="L36" t="n">
-        <v>67.83</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.985</v>
+        <v>0.052</v>
       </c>
       <c r="Q36" t="n">
-        <v>201</v>
+        <v>5072</v>
       </c>
       <c r="R36" t="n">
-        <v>5.89</v>
+        <v>33</v>
       </c>
       <c r="S36" t="n">
-        <v>31</v>
-      </c>
-      <c r="T36" t="inlineStr"/>
+        <v>-25</v>
+      </c>
+      <c r="T36" t="n">
+        <v>71</v>
+      </c>
       <c r="U36" t="n">
-        <v>35</v>
+        <v>-11</v>
       </c>
       <c r="V36" t="n">
-        <v>5.39</v>
+        <v>1.48</v>
       </c>
       <c r="W36" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="X36" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>69</v>
+      </c>
       <c r="AA36" t="n">
-        <v>263.59</v>
+        <v>111.36</v>
       </c>
       <c r="AB36" t="n">
-        <v>272.81</v>
+        <v>112.09</v>
       </c>
       <c r="AC36" t="n">
-        <v>-51.2</v>
+        <v>35.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>132.2027333333333</v>
+        <v>105.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>-3.1</v>
+        <v>19.4</v>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="AM36" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="AN36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
         <v>3</v>
       </c>
       <c r="AS36" t="n">
-        <v>19830410</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>19830410</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>19830410</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>19830410</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>19830410</v>
+        <v>78892500</v>
       </c>
       <c r="AX36" t="n">
-        <v>19830410</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>19830410</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA36" t="n">
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F37" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" t="n">
         <v>9</v>
       </c>
-      <c r="G37" t="n">
-        <v>13</v>
-      </c>
       <c r="H37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>113.54</v>
+        <v>421.7</v>
       </c>
       <c r="J37" t="n">
-        <v>111.01</v>
+        <v>446.04</v>
       </c>
       <c r="K37" t="n">
-        <v>2.3</v>
+        <v>-5.5</v>
       </c>
       <c r="L37" t="n">
-        <v>73.48</v>
+        <v>70.55</v>
       </c>
       <c r="M37" t="n">
-        <v>0.45</v>
+        <v>19.34</v>
       </c>
       <c r="N37" t="n">
         <v>8</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.209</v>
+        <v>0.535</v>
       </c>
       <c r="Q37" t="n">
-        <v>215</v>
+        <v>3616</v>
       </c>
       <c r="R37" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="S37" t="n">
+        <v>2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>127</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-14</v>
+      </c>
+      <c r="V37" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="W37" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
         <v>21</v>
       </c>
-      <c r="T37" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="U37" t="n">
-        <v>-29</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W37" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="Y37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.11</v>
-      </c>
       <c r="AA37" t="n">
-        <v>112.01</v>
+        <v>438.71</v>
       </c>
       <c r="AB37" t="n">
-        <v>118.75</v>
+        <v>431.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.2</v>
+        <v>12.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>111.3431590909091</v>
+        <v>454.2782298941436</v>
       </c>
       <c r="AE37" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>17-09-2026</t>
+        </is>
+      </c>
+      <c r="AK37" t="n">
+        <v>43</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>45</v>
+      </c>
+      <c r="AM37" t="n">
         <v>2</v>
       </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AK37" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>33</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>16</v>
-      </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AQ37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>91162330</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>91162330</v>
       </c>
       <c r="AU37" t="n">
-        <v>3936339</v>
+        <v>91162330</v>
       </c>
       <c r="AV37" t="n">
-        <v>4899099</v>
+        <v>274696140</v>
       </c>
       <c r="AW37" t="n">
-        <v>4899099</v>
+        <v>274696140</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>91162330</v>
       </c>
       <c r="AY37" t="n">
-        <v>3936339</v>
+        <v>91162330</v>
       </c>
       <c r="AZ37" t="n">
         <v>1</v>
@@ -7291,204 +7293,200 @@
         <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amanta Healthcare Limited</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G38" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>189.95</v>
+        <v>128.15</v>
       </c>
       <c r="J38" t="n">
-        <v>149.98</v>
+        <v>132.2</v>
       </c>
       <c r="K38" t="n">
-        <v>26.7</v>
+        <v>-3.1</v>
       </c>
       <c r="L38" t="n">
-        <v>63.56</v>
+        <v>67.83</v>
       </c>
       <c r="M38" t="n">
-        <v>0.24</v>
+        <v>1.98</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.033</v>
+        <v>0.985</v>
       </c>
       <c r="Q38" t="n">
-        <v>738</v>
+        <v>201</v>
       </c>
       <c r="R38" t="n">
-        <v>48.1</v>
+        <v>5.89</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
-      </c>
-      <c r="T38" t="n">
-        <v>14.54</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="n">
-        <v>-4</v>
+        <v>35</v>
       </c>
       <c r="V38" t="n">
-        <v>0.85</v>
+        <v>5.39</v>
       </c>
       <c r="W38" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="X38" t="n">
-        <v>1.11</v>
+        <v>2.89</v>
       </c>
       <c r="Y38" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>21.13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="n">
-        <v>177.79</v>
+        <v>263.59</v>
       </c>
       <c r="AB38" t="n">
-        <v>133.78</v>
+        <v>272.81</v>
       </c>
       <c r="AC38" t="n">
-        <v>94.90000000000001</v>
+        <v>-51.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>149.9802469135803</v>
+        <v>132.2027333333333</v>
       </c>
       <c r="AE38" t="n">
-        <v>26.7</v>
+        <v>-3.1</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL38" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="AM38" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>19830410</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>19830410</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>19830410</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>19830410</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>19830410</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>19830410</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>19830410</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA38" t="n">
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7499,157 +7497,149 @@
         <v>11</v>
       </c>
       <c r="F39" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="J39" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L39" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N39" t="n">
+        <v>9</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>814</v>
+      </c>
+      <c r="R39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Y39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>67.17</v>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>64.33497045790251</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>33</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ39" t="n">
         <v>12</v>
       </c>
-      <c r="G39" t="n">
+      <c r="AR39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2601121</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2601121</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>2601121</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>8710955</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>8710955</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>2601121</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>2601121</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>4</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>162.6</v>
-      </c>
-      <c r="J39" t="n">
-        <v>159.62</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="L39" t="n">
-        <v>65.64</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="P39" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1805</v>
-      </c>
-      <c r="R39" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="S39" t="n">
-        <v>-3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>26</v>
-      </c>
-      <c r="U39" t="n">
-        <v>-4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="W39" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Y39" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>179.99</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>186.95</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>-13</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>159.624192</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>Early Accumulation</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Early Accumulation</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="AK39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1</v>
       </c>
       <c r="BA39" t="n">
         <v>0</v>
@@ -7661,16 +7651,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PGHH</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Hygiene and Health Care Limited</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7678,121 +7668,121 @@
         </is>
       </c>
       <c r="E40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>13</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>113.54</v>
+      </c>
+      <c r="J40" t="n">
+        <v>111.01</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L40" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N40" t="n">
+        <v>8</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>215</v>
+      </c>
+      <c r="R40" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="S40" t="n">
+        <v>21</v>
+      </c>
+      <c r="T40" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-29</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W40" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Y40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>112.01</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>111.3431590909091</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="AK40" t="n">
         <v>17</v>
       </c>
-      <c r="F40" t="n">
-        <v>20</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I40" t="n">
-        <v>7486</v>
-      </c>
-      <c r="J40" t="n">
-        <v>8995.5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="L40" t="n">
-        <v>70.64</v>
-      </c>
-      <c r="M40" t="n">
-        <v>557.4400000000001</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>19-06-2026</t>
-        </is>
-      </c>
-      <c r="P40" t="n">
-        <v>2.294</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>24300</v>
-      </c>
-      <c r="R40" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="S40" t="n">
-        <v>-2</v>
-      </c>
-      <c r="T40" t="n">
-        <v>170</v>
-      </c>
-      <c r="U40" t="n">
-        <v>-5</v>
-      </c>
-      <c r="V40" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>157</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>8308.200000000001</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>10194.17</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>-26.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>8995.500000806864</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>19-06-2026</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>19-06-2026</t>
-        </is>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
       <c r="AL40" t="n">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="AM40" t="n">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -7801,13 +7791,13 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS40" t="n">
         <v>0</v>
@@ -7816,25 +7806,25 @@
         <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3936339</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>4899099</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>4899099</v>
       </c>
       <c r="AX40" t="n">
         <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>3936339</v>
       </c>
       <c r="AZ40" t="n">
         <v>1</v>
       </c>
       <c r="BA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
         <v>0</v>
@@ -7843,12 +7833,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>Amanta Healthcare Limited</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -7860,85 +7850,87 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>172.37</v>
+        <v>189.95</v>
       </c>
       <c r="J41" t="n">
-        <v>182.69</v>
+        <v>149.98</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.6</v>
+        <v>26.7</v>
       </c>
       <c r="L41" t="n">
-        <v>69.05</v>
+        <v>63.56</v>
       </c>
       <c r="M41" t="n">
-        <v>0.74</v>
+        <v>0.24</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.125</v>
+        <v>0.033</v>
       </c>
       <c r="Q41" t="n">
-        <v>590</v>
+        <v>738</v>
       </c>
       <c r="R41" t="n">
-        <v>14</v>
+        <v>48.1</v>
       </c>
       <c r="S41" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="T41" t="n">
-        <v>15</v>
+        <v>14.54</v>
       </c>
       <c r="U41" t="n">
-        <v>82</v>
+        <v>-4</v>
       </c>
       <c r="V41" t="n">
-        <v>3.07</v>
+        <v>0.85</v>
       </c>
       <c r="W41" t="n">
-        <v>42.7</v>
+        <v>11.6</v>
       </c>
       <c r="X41" t="n">
-        <v>0.35</v>
+        <v>1.11</v>
       </c>
       <c r="Y41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>12</v>
+        <v>21.13</v>
       </c>
       <c r="AA41" t="n">
-        <v>169.28</v>
-      </c>
-      <c r="AB41" t="inlineStr"/>
+        <v>177.79</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>133.78</v>
+      </c>
       <c r="AC41" t="n">
-        <v>-10.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AD41" t="n">
-        <v>182.6945759634963</v>
+        <v>149.9802469135803</v>
       </c>
       <c r="AE41" t="n">
-        <v>-5.7</v>
+        <v>26.7</v>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
@@ -7957,22 +7949,22 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AM41" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AN41" t="n">
         <v>0</v>
@@ -7987,7 +7979,7 @@
         <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
         <v>0</v>
@@ -8002,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>7447179</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
         <v>0</v>
@@ -8011,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA41" t="n">
         <v>0</v>
@@ -8023,12 +8015,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -8040,121 +8032,119 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G42" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>40.43</v>
+        <v>172.37</v>
       </c>
       <c r="J42" t="n">
-        <v>42.6</v>
+        <v>182.69</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.1</v>
+        <v>-5.6</v>
       </c>
       <c r="L42" t="n">
-        <v>71.79000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="M42" t="n">
-        <v>1.4</v>
+        <v>0.74</v>
       </c>
       <c r="N42" t="n">
+        <v>3</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>590</v>
+      </c>
+      <c r="R42" t="n">
+        <v>14</v>
+      </c>
+      <c r="S42" t="n">
+        <v>61</v>
+      </c>
+      <c r="T42" t="n">
+        <v>15</v>
+      </c>
+      <c r="U42" t="n">
+        <v>82</v>
+      </c>
+      <c r="V42" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="W42" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
         <v>12</v>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="P42" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>400</v>
-      </c>
-      <c r="R42" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="S42" t="n">
-        <v>246</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="U42" t="n">
-        <v>10</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="W42" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>4.21</v>
-      </c>
       <c r="AA42" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>39.8</v>
-      </c>
+        <v>169.28</v>
+      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.8</v>
+        <v>-10.9</v>
       </c>
       <c r="AD42" t="n">
-        <v>42.08691523192088</v>
+        <v>182.6945759634963</v>
       </c>
       <c r="AE42" t="n">
-        <v>-3.9</v>
+        <v>-5.7</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AK42" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="AM42" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
@@ -8163,13 +8153,13 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="AS42" t="n">
         <v>0</v>
@@ -8178,22 +8168,22 @@
         <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>21852194</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>22247438</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>22247438</v>
+        <v>7447179</v>
       </c>
       <c r="AX42" t="n">
         <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>21852194</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA42" t="n">
         <v>0</v>
@@ -8205,12 +8195,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -8222,157 +8212,157 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>51.9</v>
+        <v>162.6</v>
       </c>
       <c r="J43" t="n">
-        <v>56.66</v>
+        <v>159.62</v>
       </c>
       <c r="K43" t="n">
-        <v>-8.4</v>
+        <v>1.9</v>
       </c>
       <c r="L43" t="n">
-        <v>73.01000000000001</v>
+        <v>65.64</v>
       </c>
       <c r="M43" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>17-09-2026</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1805</v>
+      </c>
+      <c r="R43" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S43" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>26</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V43" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W43" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Y43" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>179.99</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>186.95</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>159.624192</v>
+      </c>
+      <c r="AE43" t="n">
         <v>1.9</v>
       </c>
-      <c r="N43" t="n">
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>17-09-2026</t>
+        </is>
+      </c>
+      <c r="AK43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL43" t="n">
         <v>3</v>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>16-08-2026</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>450</v>
-      </c>
-      <c r="R43" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="S43" t="n">
-        <v>19</v>
-      </c>
-      <c r="T43" t="n">
-        <v>21</v>
-      </c>
-      <c r="U43" t="n">
-        <v>20</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W43" t="n">
-        <v>12</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="Y43" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>56.75</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>58.31</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>-14.3</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>57.35626428571429</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>05-08-2026</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>16-08-2026</t>
-        </is>
-      </c>
-      <c r="AK43" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>45</v>
-      </c>
       <c r="AM43" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AR43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>39906048</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>39906048</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>39906048</v>
       </c>
       <c r="AV43" t="n">
-        <v>24089631</v>
+        <v>39906048</v>
       </c>
       <c r="AW43" t="n">
-        <v>24089631</v>
+        <v>39906048</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>39906048</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>39906048</v>
       </c>
       <c r="AZ43" t="n">
         <v>1</v>
@@ -8381,22 +8371,22 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>PGHH</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>Procter &amp; Gamble Hygiene and Health Care Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -8404,161 +8394,163 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I44" t="n">
-        <v>589.3</v>
+        <v>7486</v>
       </c>
       <c r="J44" t="n">
-        <v>593.62</v>
+        <v>8995.5</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.7</v>
+        <v>-16.8</v>
       </c>
       <c r="L44" t="n">
-        <v>74.02</v>
+        <v>70.64</v>
       </c>
       <c r="M44" t="n">
-        <v>0.25</v>
+        <v>557.4400000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.027</v>
+        <v>2.294</v>
       </c>
       <c r="Q44" t="n">
-        <v>916</v>
-      </c>
-      <c r="R44" t="inlineStr"/>
+        <v>24300</v>
+      </c>
+      <c r="R44" t="n">
+        <v>30.7</v>
+      </c>
       <c r="S44" t="n">
         <v>-2</v>
       </c>
       <c r="T44" t="n">
-        <v>5</v>
+        <v>170</v>
       </c>
       <c r="U44" t="n">
-        <v>-152</v>
+        <v>-5</v>
       </c>
       <c r="V44" t="n">
-        <v>-6.5</v>
+        <v>38.9</v>
       </c>
       <c r="W44" t="n">
-        <v>9.24</v>
+        <v>157</v>
       </c>
       <c r="X44" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="b">
         <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AA44" t="n">
-        <v>590.8</v>
+        <v>8308.200000000001</v>
       </c>
       <c r="AB44" t="n">
-        <v>545.85</v>
+        <v>10194.17</v>
       </c>
       <c r="AC44" t="n">
-        <v>17.1</v>
+        <v>-26.3</v>
       </c>
       <c r="AD44" t="n">
-        <v>593.6235208886742</v>
+        <v>8995.500000806864</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.7</v>
+        <v>-16.8</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="AK44" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="AM44" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="AN44" t="n">
         <v>0</v>
       </c>
       <c r="AO44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
         <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>1288195</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
         <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB44" t="n">
         <v>0</v>
@@ -8567,16 +8559,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -8584,119 +8576,121 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F45" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I45" t="n">
-        <v>718.8</v>
+        <v>40.43</v>
       </c>
       <c r="J45" t="n">
-        <v>815.16</v>
+        <v>42.6</v>
       </c>
       <c r="K45" t="n">
-        <v>-11.8</v>
+        <v>-5.1</v>
       </c>
       <c r="L45" t="n">
-        <v>73.2</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="Q45" t="n">
-        <v>728</v>
+        <v>400</v>
       </c>
       <c r="R45" t="n">
-        <v>13.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S45" t="n">
-        <v>185</v>
+        <v>246</v>
       </c>
       <c r="T45" t="n">
-        <v>11.55</v>
+        <v>0.91</v>
       </c>
       <c r="U45" t="n">
-        <v>204</v>
+        <v>10</v>
       </c>
       <c r="V45" t="n">
-        <v>6.84</v>
+        <v>0.14</v>
       </c>
       <c r="W45" t="n">
-        <v>50.7</v>
+        <v>2.07</v>
       </c>
       <c r="X45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>16.07</v>
+        <v>4.21</v>
       </c>
       <c r="AA45" t="n">
-        <v>729.78</v>
-      </c>
-      <c r="AB45" t="inlineStr"/>
+        <v>40.71</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>39.8</v>
+      </c>
       <c r="AC45" t="n">
-        <v>-20.9</v>
+        <v>0.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>815.1570095913809</v>
+        <v>42.08691523192088</v>
       </c>
       <c r="AE45" t="n">
-        <v>-11.8</v>
+        <v>-3.9</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AK45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AL45" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="AM45" t="n">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -8705,13 +8699,13 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR45" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AS45" t="n">
         <v>0</v>
@@ -8720,22 +8714,22 @@
         <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>21852194</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>22247438</v>
       </c>
       <c r="AW45" t="n">
-        <v>3623803</v>
+        <v>22247438</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>21852194</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA45" t="n">
         <v>0</v>
@@ -8747,16 +8741,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -8764,181 +8758,181 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F46" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H46" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="I46" t="n">
-        <v>185.4</v>
+        <v>96.86</v>
       </c>
       <c r="J46" t="n">
-        <v>207.63</v>
+        <v>98.83</v>
       </c>
       <c r="K46" t="n">
-        <v>-10.7</v>
+        <v>-2</v>
       </c>
       <c r="L46" t="n">
-        <v>74.26000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="M46" t="n">
-        <v>4.7</v>
+        <v>1.25</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.052</v>
+        <v>0.127</v>
       </c>
       <c r="Q46" t="n">
-        <v>9012</v>
+        <v>988</v>
       </c>
       <c r="R46" t="n">
-        <v>15.3</v>
+        <v>26.9</v>
       </c>
       <c r="S46" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="T46" t="n">
-        <v>224</v>
+        <v>18.68</v>
       </c>
       <c r="U46" t="n">
-        <v>38</v>
+        <v>-36</v>
       </c>
       <c r="V46" t="n">
-        <v>3.32</v>
+        <v>0.85</v>
       </c>
       <c r="W46" t="n">
-        <v>24.2</v>
+        <v>6.83</v>
       </c>
       <c r="X46" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="Y46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>41</v>
+        <v>4.02</v>
       </c>
       <c r="AA46" t="n">
-        <v>200.25</v>
+        <v>88.86</v>
       </c>
       <c r="AB46" t="n">
-        <v>209.82</v>
+        <v>101.88</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>207.6336012165256</v>
+        <v>98.83018254484323</v>
       </c>
       <c r="AE46" t="n">
-        <v>-10.7</v>
+        <v>-2</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AL46" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AM46" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>9750000</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>9750000</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>9750000</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>9750000</v>
       </c>
       <c r="AW46" t="n">
-        <v>46970458</v>
+        <v>12463079</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>9750000</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>9750000</v>
       </c>
       <c r="AZ46" t="n">
         <v>1</v>
       </c>
       <c r="BA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8946,91 +8940,89 @@
         </is>
       </c>
       <c r="E47" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" t="n">
         <v>13</v>
       </c>
-      <c r="F47" t="n">
-        <v>11</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
       <c r="H47" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>26.13</v>
+        <v>589.3</v>
       </c>
       <c r="J47" t="n">
-        <v>33.59</v>
+        <v>593.62</v>
       </c>
       <c r="K47" t="n">
-        <v>-22.2</v>
+        <v>-0.7</v>
       </c>
       <c r="L47" t="n">
-        <v>61.81</v>
+        <v>74.02</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="N47" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.254</v>
+        <v>0.027</v>
       </c>
       <c r="Q47" t="n">
-        <v>276</v>
-      </c>
-      <c r="R47" t="n">
-        <v>14.6</v>
-      </c>
+        <v>916</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="T47" t="n">
-        <v>2.79</v>
+        <v>5</v>
       </c>
       <c r="U47" t="n">
-        <v>-30</v>
+        <v>-152</v>
       </c>
       <c r="V47" t="n">
-        <v>0.21</v>
+        <v>-6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>18</v>
+        <v>9.24</v>
       </c>
       <c r="X47" t="n">
-        <v>0.32</v>
+        <v>2.23</v>
       </c>
       <c r="Y47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.83</v>
+        <v>6</v>
       </c>
       <c r="AA47" t="n">
-        <v>28.98</v>
+        <v>590.8</v>
       </c>
       <c r="AB47" t="n">
-        <v>32.45</v>
+        <v>545.85</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.2</v>
+        <v>17.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>33.59387559808612</v>
+        <v>593.6235208886742</v>
       </c>
       <c r="AE47" t="n">
-        <v>-22.2</v>
+        <v>-0.7</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
@@ -9045,82 +9037,82 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AK47" t="n">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="AL47" t="n">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="AM47" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP47" t="n">
         <v>3</v>
       </c>
-      <c r="AN47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>2</v>
-      </c>
       <c r="AQ47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR47" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AS47" t="n">
-        <v>691000</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
-        <v>691000</v>
+        <v>1288195</v>
       </c>
       <c r="AU47" t="n">
-        <v>1434750</v>
+        <v>2458195</v>
       </c>
       <c r="AV47" t="n">
-        <v>2893750</v>
+        <v>2458195</v>
       </c>
       <c r="AW47" t="n">
-        <v>7021120</v>
+        <v>2458195</v>
       </c>
       <c r="AX47" t="n">
-        <v>691000</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>1434750</v>
+        <v>2458195</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA47" t="n">
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0.4816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -9128,58 +9120,64 @@
         </is>
       </c>
       <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>26</v>
+      </c>
+      <c r="G48" t="n">
         <v>5</v>
       </c>
-      <c r="F48" t="n">
-        <v>8</v>
-      </c>
-      <c r="G48" t="n">
-        <v>9</v>
-      </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I48" t="n">
-        <v>66.26000000000001</v>
+        <v>185.4</v>
       </c>
       <c r="J48" t="n">
-        <v>64.04000000000001</v>
+        <v>207.63</v>
       </c>
       <c r="K48" t="n">
-        <v>3.5</v>
+        <v>-10.7</v>
       </c>
       <c r="L48" t="n">
-        <v>64.29000000000001</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>0.31</v>
+        <v>4.7</v>
       </c>
       <c r="N48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.038</v>
+        <v>0.052</v>
       </c>
       <c r="Q48" t="n">
-        <v>814</v>
+        <v>9012</v>
       </c>
       <c r="R48" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S48" t="inlineStr"/>
+        <v>15.3</v>
+      </c>
+      <c r="S48" t="n">
+        <v>21</v>
+      </c>
       <c r="T48" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="U48" t="inlineStr"/>
+        <v>224</v>
+      </c>
+      <c r="U48" t="n">
+        <v>38</v>
+      </c>
       <c r="V48" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W48" t="inlineStr"/>
+        <v>3.32</v>
+      </c>
+      <c r="W48" t="n">
+        <v>24.2</v>
+      </c>
       <c r="X48" t="n">
         <v>0.11</v>
       </c>
@@ -9187,54 +9185,56 @@
         <v>1</v>
       </c>
       <c r="Z48" t="n">
-        <v>12.14</v>
+        <v>41</v>
       </c>
       <c r="AA48" t="n">
-        <v>67.17</v>
-      </c>
-      <c r="AB48" t="inlineStr"/>
+        <v>200.25</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>209.82</v>
+      </c>
       <c r="AC48" t="n">
-        <v>30.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD48" t="n">
-        <v>64.04438155136269</v>
+        <v>207.6336012165256</v>
       </c>
       <c r="AE48" t="n">
-        <v>3.5</v>
+        <v>-10.7</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="AK48" t="n">
         <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="n">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="n">
         <v>0</v>
@@ -9246,10 +9246,10 @@
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AS48" t="n">
         <v>0</v>
@@ -9261,10 +9261,10 @@
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>6109834</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>6109834</v>
+        <v>46970458</v>
       </c>
       <c r="AX48" t="n">
         <v>0</v>
@@ -9273,10 +9273,10 @@
         <v>0</v>
       </c>
       <c r="AZ48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB48" t="n">
         <v>0</v>
@@ -9285,16 +9285,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Studds Accessories Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -9302,91 +9302,91 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
+        <v>11</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="J49" t="n">
+        <v>33.59</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N49" t="n">
+        <v>9</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>276</v>
+      </c>
+      <c r="R49" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="S49" t="n">
         <v>16</v>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>407.1</v>
-      </c>
-      <c r="J49" t="n">
-        <v>417.34</v>
-      </c>
-      <c r="K49" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="L49" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>11-09-2026</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1602</v>
-      </c>
-      <c r="R49" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
       <c r="T49" t="n">
-        <v>20</v>
+        <v>2.79</v>
       </c>
       <c r="U49" t="n">
-        <v>2</v>
+        <v>-30</v>
       </c>
       <c r="V49" t="n">
-        <v>3.37</v>
+        <v>0.21</v>
       </c>
       <c r="W49" t="n">
-        <v>23.3</v>
+        <v>18</v>
       </c>
       <c r="X49" t="n">
-        <v>0.01</v>
+        <v>0.32</v>
       </c>
       <c r="Y49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>12</v>
+        <v>1.83</v>
       </c>
       <c r="AA49" t="n">
-        <v>438.15</v>
+        <v>28.98</v>
       </c>
       <c r="AB49" t="n">
-        <v>482.09</v>
+        <v>32.45</v>
       </c>
       <c r="AC49" t="n">
-        <v>-20.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD49" t="n">
-        <v>417.3421638870492</v>
+        <v>33.59387559808612</v>
       </c>
       <c r="AE49" t="n">
-        <v>-2.5</v>
+        <v>-22.2</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
@@ -9401,58 +9401,58 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AL49" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="AM49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP49" t="n">
         <v>2</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AR49" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>691000</v>
       </c>
       <c r="AT49" t="n">
-        <v>13863272</v>
+        <v>691000</v>
       </c>
       <c r="AU49" t="n">
-        <v>13863272</v>
+        <v>1434750</v>
       </c>
       <c r="AV49" t="n">
-        <v>13863272</v>
+        <v>2893750</v>
       </c>
       <c r="AW49" t="n">
-        <v>13863272</v>
+        <v>7021120</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>691000</v>
       </c>
       <c r="AY49" t="n">
-        <v>13863272</v>
+        <v>1434750</v>
       </c>
       <c r="AZ49" t="n">
         <v>1</v>
@@ -9461,22 +9461,22 @@
         <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>0.4816</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>Studds Accessories Limited</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -9484,157 +9484,157 @@
         </is>
       </c>
       <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>16</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>407.1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>417.34</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="L50" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1602</v>
+      </c>
+      <c r="R50" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="n">
+        <v>20</v>
+      </c>
+      <c r="U50" t="n">
         <v>2</v>
       </c>
-      <c r="F50" t="n">
-        <v>7</v>
-      </c>
-      <c r="G50" t="n">
-        <v>9</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I50" t="n">
-        <v>96.86</v>
-      </c>
-      <c r="J50" t="n">
-        <v>103.93</v>
-      </c>
-      <c r="K50" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="L50" t="n">
-        <v>71.89</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>30-06-2026</t>
-        </is>
-      </c>
-      <c r="P50" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>988</v>
-      </c>
-      <c r="R50" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="S50" t="n">
-        <v>9</v>
-      </c>
-      <c r="T50" t="n">
-        <v>18.68</v>
-      </c>
-      <c r="U50" t="n">
-        <v>-36</v>
-      </c>
       <c r="V50" t="n">
-        <v>0.85</v>
+        <v>3.37</v>
       </c>
       <c r="W50" t="n">
-        <v>6.83</v>
+        <v>23.3</v>
       </c>
       <c r="X50" t="n">
-        <v>0.26</v>
+        <v>0.01</v>
       </c>
       <c r="Y50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z50" t="n">
-        <v>4.02</v>
+        <v>12</v>
       </c>
       <c r="AA50" t="n">
-        <v>88.86</v>
+        <v>438.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>101.88</v>
+        <v>482.09</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.3</v>
+        <v>-20.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>103.9254960545468</v>
+        <v>417.3421638870492</v>
       </c>
       <c r="AE50" t="n">
-        <v>-6.8</v>
+        <v>-2.5</v>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AK50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="AM50" t="n">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="AN50" t="n">
         <v>0</v>
       </c>
       <c r="AO50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS50" t="n">
         <v>0</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>13863272</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>13863272</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>13863272</v>
       </c>
       <c r="AW50" t="n">
-        <v>2713079</v>
+        <v>13863272</v>
       </c>
       <c r="AX50" t="n">
         <v>0</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>13863272</v>
       </c>
       <c r="AZ50" t="n">
         <v>1</v>
@@ -10155,70 +10155,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>91.05</v>
+        <v>654.2</v>
       </c>
       <c r="D4" t="n">
-        <v>75.68000000000001</v>
+        <v>619.77</v>
       </c>
       <c r="E4" t="n">
-        <v>20.3</v>
+        <v>5.6</v>
       </c>
       <c r="F4" t="n">
-        <v>74.84999999999999</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>3.14</v>
+        <v>4.88</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>69.98999999999999</v>
+        <v>91.05</v>
       </c>
       <c r="D5" t="n">
-        <v>74.56</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.1</v>
+        <v>20.3</v>
       </c>
       <c r="F5" t="n">
-        <v>72.56999999999999</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.85</v>
+        <v>3.14</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
     </row>
@@ -10260,66 +10260,66 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>102.63</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>92.77</v>
+        <v>74.56</v>
       </c>
       <c r="E7" t="n">
-        <v>10.6</v>
+        <v>-6.1</v>
       </c>
       <c r="F7" t="n">
-        <v>70.88</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>9.710000000000001</v>
+        <v>1.85</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>654.2</v>
+        <v>102.63</v>
       </c>
       <c r="D8" t="n">
-        <v>617.65</v>
+        <v>92.77</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9</v>
+        <v>10.6</v>
       </c>
       <c r="F8" t="n">
-        <v>64.68000000000001</v>
+        <v>70.88</v>
       </c>
       <c r="G8" t="n">
-        <v>4.46</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -11100,35 +11100,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BERGER PAINTS (I) LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>458.65</v>
+        <v>51.9</v>
       </c>
       <c r="D31" t="n">
-        <v>489.56</v>
+        <v>56.04</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.3</v>
+        <v>-7.4</v>
       </c>
       <c r="F31" t="n">
-        <v>75</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>4.84</v>
+        <v>2.19</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>
@@ -11170,101 +11170,101 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>BERGER PAINTS (I) LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>12.46</v>
+        <v>458.65</v>
       </c>
       <c r="D33" t="n">
-        <v>12.86</v>
+        <v>489.56</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.1</v>
+        <v>-6.3</v>
       </c>
       <c r="F33" t="n">
-        <v>69.12</v>
+        <v>75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.35</v>
+        <v>4.84</v>
       </c>
       <c r="H33" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>125.64</v>
+        <v>12.46</v>
       </c>
       <c r="D34" t="n">
-        <v>105.19</v>
+        <v>12.86</v>
       </c>
       <c r="E34" t="n">
-        <v>19.4</v>
+        <v>-3.1</v>
       </c>
       <c r="F34" t="n">
-        <v>67.15000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="G34" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>421.7</v>
+        <v>718.8</v>
       </c>
       <c r="D35" t="n">
-        <v>446.04</v>
+        <v>799.47</v>
       </c>
       <c r="E35" t="n">
-        <v>-5.5</v>
+        <v>-10.1</v>
       </c>
       <c r="F35" t="n">
-        <v>70.55</v>
+        <v>73.2</v>
       </c>
       <c r="G35" t="n">
-        <v>19.34</v>
+        <v>1.42</v>
       </c>
       <c r="H35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -11275,525 +11275,525 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>128.15</v>
+        <v>125.64</v>
       </c>
       <c r="D36" t="n">
-        <v>132.2</v>
+        <v>105.19</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.1</v>
+        <v>19.4</v>
       </c>
       <c r="F36" t="n">
-        <v>67.83</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>113.54</v>
+        <v>421.7</v>
       </c>
       <c r="D37" t="n">
-        <v>111.01</v>
+        <v>446.04</v>
       </c>
       <c r="E37" t="n">
-        <v>2.3</v>
+        <v>-5.5</v>
       </c>
       <c r="F37" t="n">
-        <v>73.48</v>
+        <v>70.55</v>
       </c>
       <c r="G37" t="n">
-        <v>0.45</v>
+        <v>19.34</v>
       </c>
       <c r="H37" t="n">
         <v>8</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Amanta Healthcare Limited</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>189.95</v>
+        <v>128.15</v>
       </c>
       <c r="D38" t="n">
-        <v>149.98</v>
+        <v>132.2</v>
       </c>
       <c r="E38" t="n">
-        <v>26.7</v>
+        <v>-3.1</v>
       </c>
       <c r="F38" t="n">
-        <v>63.56</v>
+        <v>67.83</v>
       </c>
       <c r="G38" t="n">
-        <v>0.24</v>
+        <v>1.98</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>162.6</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>159.62</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="F39" t="n">
-        <v>65.64</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>3.99</v>
+        <v>0.57</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PGHH</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Hygiene and Health Care Limited</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7486</v>
+        <v>113.54</v>
       </c>
       <c r="D40" t="n">
-        <v>8995.5</v>
+        <v>111.01</v>
       </c>
       <c r="E40" t="n">
-        <v>-16.8</v>
+        <v>2.3</v>
       </c>
       <c r="F40" t="n">
-        <v>70.64</v>
+        <v>73.48</v>
       </c>
       <c r="G40" t="n">
-        <v>557.4400000000001</v>
+        <v>0.45</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>Amanta Healthcare Limited</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>172.37</v>
+        <v>189.95</v>
       </c>
       <c r="D41" t="n">
-        <v>182.69</v>
+        <v>149.98</v>
       </c>
       <c r="E41" t="n">
-        <v>-5.6</v>
+        <v>26.7</v>
       </c>
       <c r="F41" t="n">
-        <v>69.05</v>
+        <v>63.56</v>
       </c>
       <c r="G41" t="n">
-        <v>0.74</v>
+        <v>0.24</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>40.43</v>
+        <v>172.37</v>
       </c>
       <c r="D42" t="n">
-        <v>42.6</v>
+        <v>182.69</v>
       </c>
       <c r="E42" t="n">
-        <v>-5.1</v>
+        <v>-5.6</v>
       </c>
       <c r="F42" t="n">
-        <v>71.79000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="G42" t="n">
-        <v>1.4</v>
+        <v>0.74</v>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>51.9</v>
+        <v>162.6</v>
       </c>
       <c r="D43" t="n">
-        <v>56.66</v>
+        <v>159.62</v>
       </c>
       <c r="E43" t="n">
-        <v>-8.4</v>
+        <v>1.9</v>
       </c>
       <c r="F43" t="n">
-        <v>73.01000000000001</v>
+        <v>65.64</v>
       </c>
       <c r="G43" t="n">
-        <v>1.9</v>
+        <v>3.99</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>16-08-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>PGHH</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>Procter &amp; Gamble Hygiene and Health Care Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>589.3</v>
+        <v>7486</v>
       </c>
       <c r="D44" t="n">
-        <v>593.62</v>
+        <v>8995.5</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.7</v>
+        <v>-16.8</v>
       </c>
       <c r="F44" t="n">
-        <v>74.02</v>
+        <v>70.64</v>
       </c>
       <c r="G44" t="n">
-        <v>0.25</v>
+        <v>557.4400000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>718.8</v>
+        <v>40.43</v>
       </c>
       <c r="D45" t="n">
-        <v>815.16</v>
+        <v>42.6</v>
       </c>
       <c r="E45" t="n">
-        <v>-11.8</v>
+        <v>-5.1</v>
       </c>
       <c r="F45" t="n">
-        <v>73.2</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>185.4</v>
+        <v>96.86</v>
       </c>
       <c r="D46" t="n">
-        <v>207.63</v>
+        <v>98.83</v>
       </c>
       <c r="E46" t="n">
-        <v>-10.7</v>
+        <v>-2</v>
       </c>
       <c r="F46" t="n">
-        <v>74.26000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="G46" t="n">
-        <v>4.7</v>
+        <v>1.25</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>26.13</v>
+        <v>589.3</v>
       </c>
       <c r="D47" t="n">
-        <v>33.59</v>
+        <v>593.62</v>
       </c>
       <c r="E47" t="n">
-        <v>-22.2</v>
+        <v>-0.7</v>
       </c>
       <c r="F47" t="n">
-        <v>61.81</v>
+        <v>74.02</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="H47" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>66.26000000000001</v>
+        <v>185.4</v>
       </c>
       <c r="D48" t="n">
-        <v>64.04000000000001</v>
+        <v>207.63</v>
       </c>
       <c r="E48" t="n">
-        <v>3.5</v>
+        <v>-10.7</v>
       </c>
       <c r="F48" t="n">
-        <v>64.29000000000001</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.31</v>
+        <v>4.7</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Studds Accessories Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>407.1</v>
+        <v>26.13</v>
       </c>
       <c r="D49" t="n">
-        <v>417.34</v>
+        <v>33.59</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.5</v>
+        <v>-22.2</v>
       </c>
       <c r="F49" t="n">
-        <v>61.75</v>
+        <v>61.81</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>Studds Accessories Limited</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>96.86</v>
+        <v>407.1</v>
       </c>
       <c r="D50" t="n">
-        <v>103.93</v>
+        <v>417.34</v>
       </c>
       <c r="E50" t="n">
-        <v>-6.8</v>
+        <v>-2.5</v>
       </c>
       <c r="F50" t="n">
-        <v>71.89</v>
+        <v>61.75</v>
       </c>
       <c r="G50" t="n">
-        <v>0.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
@@ -11950,7 +11950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -11970,7 +11970,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
